--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_prebrut_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_prebrut_a_2020.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:07</t>
+    <t xml:space="preserve">2026-09-24 00:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -603,7 +603,7 @@
         <v>-0.02</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -614,10 +614,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -631,7 +631,7 @@
         <v>-0.07</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11">
@@ -645,7 +645,7 @@
         <v>-0.13</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12">
